--- a/excel_reports/backtest_compare/s4/compare_s4_ALL_20260528_0800_20260608_1000.xlsx
+++ b/excel_reports/backtest_compare/s4/compare_s4_ALL_20260528_0800_20260608_1000.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Live Only'!$A$1:$BK$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backtest Only'!$A$1:$BK$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Matches'!$A$1:$BK$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-15 22:05:34</t>
+          <t>2026-06-19 17:06:09</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4820,124 +4820,8 @@
         <v>46170.37509259259</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>live_s14_family</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>-1.84</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>46176.96833333333</v>
-      </c>
-      <c r="G14" s="11" t="n">
-        <v>46177.36047453704</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>live_s14_family</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>-0.64</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>46170.37509259259</v>
-      </c>
-      <c r="G15" s="11" t="n">
-        <v>46170.37509259259</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>bt_s14_family</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>-71.95999999999999</v>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>46170.875</v>
-      </c>
-      <c r="G16" s="11" t="n">
-        <v>46181.33888888889</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>bt_s14_family</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="F17" s="11" t="n">
-        <v>46177.5</v>
-      </c>
-      <c r="G17" s="11" t="n">
-        <v>46177.5</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G17"/>
+  <autoFilter ref="A1:G13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>